--- a/data/visits/Visits_2026-09-29.xlsx
+++ b/data/visits/Visits_2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,15 +435,15 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -619,7 +619,7 @@
         <v>67.0336379</v>
       </c>
       <c r="N2" t="n">
-        <v>12.4040002822876</v>
+        <v>12.40400028</v>
       </c>
       <c r="O2" t="n">
         <v>0.6</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>00:03:16</t>
+          <t>0:03:16</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -654,8 +654,164 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIS-20260929115357-99481A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4970</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Adnan Afzaal Siddiqui</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>116674</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:53:57</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24.8369912</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.0336408</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.25899982</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:54:34</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>24.8369902</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.0336413</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.1619997</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0:00:37</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>140.3</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VIS-20260929122937-9C281F</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>116674</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:29:37</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24.8338565826416</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.03367614746094</v>
+      </c>
+      <c r="J4" t="n">
+        <v>200</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V2"/>
+  <autoFilter ref="A1:V4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-29.xlsx
+++ b/data/visits/Visits_2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -753,20 +753,16 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C4" t="n">
+        <v>3645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>116674</t>
-        </is>
+      <c r="E4" t="n">
+        <v>116674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -779,39 +775,131 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>24.8338565826416</v>
+        <v>24.83385658</v>
       </c>
       <c r="I4" t="n">
-        <v>67.03367614746094</v>
+        <v>67.03367615000001</v>
       </c>
       <c r="J4" t="n">
         <v>200</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:30:04</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>24.83385658</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67.03367615000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>200</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0:00:27</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T4" t="n">
         <v>213.4</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>213.4</v>
+      </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VIS-20260929125636-9D1A02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Adnan Afzaal Siddiqui</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>116674</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:56:36</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>24.8338565826416</v>
+      </c>
+      <c r="I5" t="n">
+        <v>67.03367614746094</v>
+      </c>
+      <c r="J5" t="n">
+        <v>200</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V4"/>
+  <autoFilter ref="A1:V5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>